--- a/test_data/test_data.xlsx
+++ b/test_data/test_data.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="properties" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="properties" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="units" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tenants" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tenant_documents" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_tenants" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="leases" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rent_payments" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
@@ -431,66 +431,191 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Section</t>
+          <t>username</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>is_email_verified</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>is_phone_verified</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OVERVIEW</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>This Excel file contains sample test data for the Asset Management Platform database. Modify the data in respective sheets to customize your test environment.</t>
+          <t>admin@assetplatform.com</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>admin123</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+91-9876543210</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HOW TO MODIFY</t>
+          <t>john_owner</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1. DO NOT modify column headers (first row) in any sheet. 2. Add/remove rows as needed for your test data. 3. All data is stored as strings to preserve formatting. 4. Empty cells will be treated as NULL in database.</t>
+          <t>john.doe@example.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>password123</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+91-9876543211</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TABLES OVERVIEW</t>
+          <t>sarah_owner</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>users - User accounts with authentication, properties - Property listings with details, tenants - Tenant information and profiles, tenant_documents - Document verification records, leases - Rental agreements and terms, rent_payments - Payment history and status.</t>
+          <t>sarah.wilson@example.com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>password123</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+91-9876543212</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IMPORTANT NOTES</t>
+          <t>manager1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>• All IDs are auto-generated UUIDs - leave empty. • Dates should be in YYYY-MM-DD format. • Boolean values: use "true" or "false" (lowercase). • JSON fields: use valid JSON string format. • Passwords will be automatically hashed during seeding.</t>
+          <t>manager@assetplatform.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>manager123</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+91-9876543213</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
@@ -505,191 +630,334 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>password</t>
+          <t>property_type</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>address_street</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_email_verified</t>
+          <t>address_city</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>is_phone_verified</t>
+          <t>address_state</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>address_pincode</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>address_landmark</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>total_floors</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>parking_spaces</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>owner_username</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>total_area</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>year_built</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>building_amenities</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>building_photos</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Modern 2BHK Apartment</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>admin@assetplatform.com</t>
+          <t>Beautiful modern apartment with great amenities</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>admin123</t>
+          <t>apartment</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+91-9876543210</t>
+          <t>available</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>123 MG Road</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>560001</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Near Brigade Road</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>john_owner</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>["wifi", "parking", "security", "gym", "swimming_pool"]</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>["building1.jpg", "building2.jpg"]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>john_owner</t>
+          <t>Luxury 3BHK Villa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>john.doe@example.com</t>
+          <t>Spacious villa with garden and modern amenities</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>villa</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+91-9876543211</t>
+          <t>available</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>456 Richmond Road</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>560025</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Near Richmond Circle</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>sarah_owner</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>["parking", "security"]</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>["building3.jpg"]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sarah_owner</t>
+          <t>Cozy 1BHK Studio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sarah.wilson@example.com</t>
+          <t>Perfect for single professionals or couples</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>password123</t>
+          <t>apartment</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+91-9876543212</t>
+          <t>rented</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>789 Commercial Street</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>manager1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>manager@assetplatform.com</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>manager123</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+91-9876543213</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>user</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>true</t>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>560001</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Near Shivaji Nagar</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>john_owner</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>["wifi", "parking", "gym"]</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>["building4.jpg", "building5.jpg"]</t>
         </is>
       </c>
     </row>
@@ -704,123 +972,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>property_name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>unit_number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>unit_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>property_type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>unit_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>address_street</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>address_city</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>address_state</t>
+          <t>floor</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>address_pincode</t>
+          <t>area</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>address_landmark</t>
+          <t>bedrooms</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>bathrooms</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>bedrooms</t>
+          <t>balconies</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>bathrooms</t>
+          <t>furnished</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>balconies</t>
+          <t>monthly_rent</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>floor</t>
+          <t>security_deposit</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>total_floors</t>
+          <t>maintenance_charges</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>furnished</t>
+          <t>unit_amenities</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>parking_spaces</t>
+          <t>unit_photos</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>monthly_rent</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>security_deposit</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>maintenance_charges</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>owner_username</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>amenities</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>photos</t>
+          <t>max_occupants</t>
         </is>
       </c>
     </row>
@@ -832,347 +1075,428 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Beautiful modern apartment with great amenities</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Modern 2BHK Apartment - Unit 101</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Beautiful 2BHK apartment with modern amenities</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>apartment</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>available</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>123 MG Road</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Karnataka</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>560001</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Near Brigade Road</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1200.00</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>45000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>135000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2000</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>["wifi", "parking", "ac", "tv"]</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>45000.00</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>135000.00</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2000.00</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>john_owner</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>["wifi", "parking", "security", "gym", "swimming_pool"]</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>["photo1.jpg", "photo2.jpg", "photo3.jpg"]</t>
-        </is>
+          <t>["unit101-1.jpg", "unit101-2.jpg"]</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Luxury 3BHK Villa</t>
+          <t>Modern 2BHK Apartment</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spacious villa with garden and modern amenities</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>villa</t>
+          <t>Modern 2BHK Apartment - Unit 102</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>Spacious 2BHK with city view</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>456 Richmond Road</t>
+          <t>apartment</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Karnataka</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>560025</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Near Richmond Circle</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2500.00</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>occupied</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>126000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2000</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>["wifi", "parking"]</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>85000.00</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>255000.00</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>5000.00</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>sarah_owner</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>["wifi", "parking", "security", "garden", "servant_quarters"]</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>["villa1.jpg", "villa2.jpg", "villa3.jpg"]</t>
-        </is>
+          <t>["unit102-1.jpg"]</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Modern 2BHK Apartment</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Modern 2BHK Apartment - Unit 201</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Premium 2BHK on higher floor</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>48000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>144000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>["wifi", "parking", "gym_access"]</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>["unit201-1.jpg", "unit201-2.jpg"]</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Luxury 3BHK Villa</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Villa-A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Luxury Villa Complex - Villa-A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Luxury villa with garden</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>villa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>255000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>["wifi", "parking", "garden", "pool"]</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>["villa-a-1.jpg", "villa-a-2.jpg"]</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Luxury 3BHK Villa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Villa-B</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Luxury Villa Complex - Villa-B</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Premium villa with pool access</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>villa</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>occupied</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>234000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4500</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>["wifi", "parking"]</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>["villa-b-1.jpg"]</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Cozy 1BHK Studio</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Perfect for single professionals or couples</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>apartment</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>rented</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>789 Commercial Street</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Karnataka</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>560001</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Near Shivaji Nagar</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>600.00</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>25000.00</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>75000.00</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1000.00</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>john_owner</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>["wifi", "parking", "security"]</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>["studio1.jpg", "studio2.jpg"]</t>
-        </is>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Office-1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Premium Office Spaces - Office-1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Modern office space</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>800</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>35000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>105000</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>["wifi", "ac", "parking"]</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>["office-1.jpg"]</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1186,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1305,11 +1629,6 @@
           <t>total_rentals</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>current_property_name</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1427,7 +1746,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1545,7 +1863,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1661,11 +1978,6 @@
       <c r="W4" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Cozy 1BHK Studio</t>
         </is>
       </c>
     </row>
@@ -1680,38 +1992,125 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>property_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unit_number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>tenant_email</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>document_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>document_number</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>file_url</t>
+          <t>is_primary_tenant</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>move_in_date</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>verified_by_username</t>
+          <t>move_out_date</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>monthly_rent_share</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>security_deposit_share</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Modern 2BHK Apartment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>rajesh.kumar@example.com</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>42000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>126000</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Luxury 3BHK Villa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Villa-B</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>priya.sharma@example.com</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>78000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>234000</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -1726,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1737,97 +2136,158 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>tenant_email</t>
+          <t>unit_number</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>primary_tenant_email</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>start_date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>notice_period_days</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>auto_renewal</t>
+          <t>monthly_rent</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>monthly_rent</t>
+          <t>security_deposit</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>security_deposit</t>
+          <t>status</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>maintenance_charges</t>
+          <t>lease_terms</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>payment_frequency</t>
+          <t>signed_at</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>rent_due_day</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>electricity_charges</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>water_charges</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>other_charges</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>pets_allowed</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>smoking_allowed</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>subletting_allowed</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>special_conditions</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>signed_at</t>
+          <t>created_by_username</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Modern 2BHK Apartment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>rajesh.kumar@example.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>42000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>126000</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Standard lease terms apply</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>john_owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Luxury 3BHK Villa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Villa-B</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>priya.sharma@example.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>78000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>234000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Premium lease with additional amenities</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2024-01-25</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>sarah_owner</t>
         </is>
       </c>
     </row>
@@ -1842,88 +2302,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>lease_id</t>
+          <t>property_name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>unit_number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>primary_tenant_email</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tenant_email</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>due_date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>paid_date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>payment_method</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>transaction_id</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>payment_reference</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>late_fee</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>penalty_amount</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>rent_amount</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>maintenance_charges</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>other_charges</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
           <t>created_by_username</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>updated_by_username</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Modern 2BHK Apartment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>rajesh.kumar@example.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>rajesh.kumar@example.com</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>February rent payment</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>john_owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Luxury 3BHK Villa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Villa-B</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>priya.sharma@example.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>priya.sharma@example.com</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>78000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>March rent payment</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>sarah_owner</t>
         </is>
       </c>
     </row>
